--- a/plantillas_excel/30_valorizacion_madre.xlsx
+++ b/plantillas_excel/30_valorizacion_madre.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -670,6 +670,26 @@
           <t>ESTADO</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SERVICIOS_PKG</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SERVICIOS_SKIP</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -726,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -807,6 +827,21 @@
       <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Hoja de salida — la completa el script. No hace falta escribir nada acá.</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>SERVICE TYPE</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MARKUP JSON</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>PRICE CODE</t>
         </is>
       </c>
     </row>
